--- a/dataproduct.api/wwwroot/templates/HRC1_BBSL_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC1_BBSL_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81728D6F-433D-49BA-912E-2FD3AC96BE78}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67F9A16-B452-473C-ADEF-F7C66A40BD8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -82,19 +82,6 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -111,6 +98,19 @@
     <font>
       <i/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -175,22 +175,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -584,16 +584,16 @@
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
@@ -605,13 +605,13 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
